--- a/servers/prospect-list-builder-micro-service/src/main/resources/filteredList.xlsx
+++ b/servers/prospect-list-builder-micro-service/src/main/resources/filteredList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brendenchoate/dev/demo/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845FB32F-C238-C247-A79F-91C185C3756A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA49B601-1790-084E-B96F-21C681714E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{BC8D8658-09BF-3A4E-A0AE-3D84FA593726}"/>
   </bookViews>
@@ -36,27 +36,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>jain Doe</t>
-  </si>
-  <si>
-    <t>john doe</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>jain@example.com</t>
-  </si>
-  <si>
-    <t>jane@example.com</t>
-  </si>
-  <si>
-    <t>Decision Maker</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t xml:space="preserve">Follow-Up Calls </t>
+  </si>
+  <si>
+    <t>Phone number</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>larry</t>
+  </si>
+  <si>
+    <t>999-999-999</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>777-777-7777</t>
+  </si>
+  <si>
+    <t>Bill</t>
   </si>
 </sst>
 </file>
@@ -446,6 +452,7 @@
     <col min="1" max="1" width="10.83203125" style="1"/>
     <col min="2" max="2" width="17.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -453,38 +460,38 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
+      <c r="C2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{0921CE29-DF95-AA44-A71E-8976E35B524D}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{5FDAE81D-8386-2442-814E-B7350B793297}"/>
+    <hyperlink ref="B2" r:id="rId1" display="Jain1@example.com" xr:uid="{0921CE29-DF95-AA44-A71E-8976E35B524D}"/>
+    <hyperlink ref="B3" r:id="rId2" display="john1@example.com" xr:uid="{5FDAE81D-8386-2442-814E-B7350B793297}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
